--- a/lorenzo-playwright-kdf/excelFramework/testcases/ePMA/LSTP_ePMA_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/ePMA/LSTP_ePMA_WF001.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tk32\ORBIS PAS UKI-LZO\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\ePMA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\ePMA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C00C39-1F9C-4A19-B136-E51E0CD00D33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B7568B6-E73B-4F24-B22D-8C672B6135E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E0691EBA-01F0-40FD-B574-1F0823951DC7}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E0691EBA-01F0-40FD-B574-1F0823951DC7}"/>
   </bookViews>
   <sheets>
     <sheet name="TestExecution" sheetId="1" r:id="rId1"/>
@@ -2628,7 +2628,7 @@
         <v>252</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>253</v>
@@ -7838,7 +7838,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{AAAB6893-DA61-4F80-A89E-42C00F47E1C9}">
           <x14:formula1>
-            <xm:f>IF(ISBLANK([LSTP_IP_WF001_8.44.xlsx]TestExecution!#REF!), INDIRECT("keywordnotreqpage"), IF(ISBLANK(#REF!), INDIRECT("keywordnotreqelement"), INDIRECT(LEFT(#REF!,3)&amp;"")))</xm:f>
+            <xm:f>IF(ISBLANK('C:\playright tutorial\[LSTP_IP_WF001_8.44.xlsx]TestExecution'!#REF!), INDIRECT("keywordnotreqpage"), IF(ISBLANK(#REF!), INDIRECT("keywordnotreqelement"), INDIRECT(LEFT(#REF!,3)&amp;"")))</xm:f>
           </x14:formula1>
           <xm:sqref>F74</xm:sqref>
         </x14:dataValidation>

--- a/lorenzo-playwright-kdf/excelFramework/testcases/ePMA/LSTP_ePMA_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/ePMA/LSTP_ePMA_WF001.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\ePMA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B7568B6-E73B-4F24-B22D-8C672B6135E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E1866A5-3075-4329-9AA6-AA0088AFC532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E0691EBA-01F0-40FD-B574-1F0823951DC7}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{E0691EBA-01F0-40FD-B574-1F0823951DC7}"/>
   </bookViews>
   <sheets>
     <sheet name="TestExecution" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1217" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="567">
   <si>
     <t>StepNo</t>
   </si>
@@ -1537,36 +1537,12 @@
     <t>Click Search to open medication search panel for Med1-Paracetamol</t>
   </si>
   <si>
-    <t>verifyMedicationChart</t>
-  </si>
-  <si>
-    <t>tbl_Columnname</t>
-  </si>
-  <si>
     <t>USERNAME</t>
   </si>
   <si>
     <t>PASSWORD</t>
   </si>
   <si>
-    <t>//wait for element</t>
-  </si>
-  <si>
-    <t>//Click on Finish in PDS Sync</t>
-  </si>
-  <si>
-    <t>//Click on Allocate NHS YES</t>
-  </si>
-  <si>
-    <t>//Click on No in Has this person had NHS No pop up</t>
-  </si>
-  <si>
-    <t>//Select the Due now option from Med chart</t>
-  </si>
-  <si>
-    <t>txt_Duenow1</t>
-  </si>
-  <si>
     <t>chk_NoWitnessAvailable</t>
   </si>
   <si>
@@ -1579,12 +1555,6 @@
     <t>equal</t>
   </si>
   <si>
-    <t>07-Jul-2026</t>
-  </si>
-  <si>
-    <t>Due now</t>
-  </si>
-  <si>
     <t>txt_Duenow</t>
   </si>
   <si>
@@ -1624,9 +1594,6 @@
     <t>Click green copy icon to copy Med3 sodium bicarbonate to IP list for modification</t>
   </si>
   <si>
-    <t>//waiting for popup click on button</t>
-  </si>
-  <si>
     <t>500</t>
   </si>
   <si>
@@ -1775,6 +1742,18 @@
   </si>
   <si>
     <t>Click on My Work tab</t>
+  </si>
+  <si>
+    <t>Click on Allocate NHS YES</t>
+  </si>
+  <si>
+    <t>Click on No in Has this person had NHS No pop up</t>
+  </si>
+  <si>
+    <t>Click on Finish in PDS Sync</t>
+  </si>
+  <si>
+    <t>waiting for popup click on button</t>
   </si>
 </sst>
 </file>
@@ -1920,7 +1899,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1978,15 +1957,6 @@
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="15" fontId="2" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="15" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="20" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -2520,7 +2490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F7ADEC0-586C-43E1-A9C1-2003481904C6}">
-  <dimension ref="A1:N280"/>
+  <dimension ref="A1:N259"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="24" bestFit="1" customWidth="1"/>
@@ -2593,7 +2563,7 @@
       <c r="I2" s="5"/>
       <c r="J2" s="5"/>
       <c r="K2" s="24" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -2617,7 +2587,7 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="K3" s="24" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -2671,7 +2641,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>573</v>
+        <v>562</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>12</v>
@@ -2742,7 +2712,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>12</v>
@@ -2961,7 +2931,7 @@
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
       <c r="K17" s="19" t="s">
-        <v>543</v>
+        <v>532</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -3034,7 +3004,7 @@
       <c r="I20" s="5"/>
       <c r="J20" s="7"/>
       <c r="K20" s="19" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -3230,7 +3200,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>500</v>
+        <v>563</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>296</v>
@@ -3253,7 +3223,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>501</v>
+        <v>564</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>296</v>
@@ -3529,7 +3499,7 @@
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
       <c r="K41" s="24" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -3867,7 +3837,7 @@
       <c r="I55" s="5"/>
       <c r="J55" s="10"/>
       <c r="K55" s="24" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -4323,7 +4293,7 @@
         <v>381</v>
       </c>
       <c r="K75" s="21" t="s">
-        <v>547</v>
+        <v>536</v>
       </c>
       <c r="N75" s="21"/>
     </row>
@@ -4351,7 +4321,7 @@
         <v>384</v>
       </c>
       <c r="K76" s="21" t="s">
-        <v>548</v>
+        <v>537</v>
       </c>
     </row>
     <row r="77" spans="1:14" ht="19.5" x14ac:dyDescent="0.25">
@@ -4378,7 +4348,7 @@
         <v>387</v>
       </c>
       <c r="K77" s="21" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
@@ -4472,7 +4442,7 @@
       <c r="I81" s="5"/>
       <c r="J81" s="5"/>
       <c r="K81" s="5" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -4727,7 +4697,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>498</v>
+        <v>295</v>
       </c>
       <c r="C93" s="5" t="s">
         <v>437</v>
@@ -4748,7 +4718,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>499</v>
+        <v>565</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>437</v>
@@ -4987,7 +4957,7 @@
       <c r="I105" s="15"/>
       <c r="J105" s="15"/>
       <c r="K105" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -5662,7 +5632,7 @@
       </c>
       <c r="J143" s="27"/>
       <c r="K143" s="32" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="L143" s="32"/>
     </row>
@@ -5684,7 +5654,7 @@
       </c>
       <c r="J144" s="27"/>
       <c r="K144" s="32" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
@@ -5705,7 +5675,7 @@
       </c>
       <c r="J145" s="27"/>
       <c r="K145" s="32" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
@@ -5726,7 +5696,7 @@
       </c>
       <c r="J146" s="27"/>
       <c r="K146" s="32" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
@@ -5825,7 +5795,7 @@
         <v>432</v>
       </c>
       <c r="K152" s="1" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
@@ -5878,7 +5848,7 @@
         <v>155</v>
       </c>
       <c r="B156" s="24" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="C156" s="15" t="s">
         <v>428</v>
@@ -5925,8 +5895,8 @@
       <c r="H158" s="5"/>
       <c r="I158" s="5"/>
       <c r="J158" s="5"/>
-      <c r="K158" s="43" t="s">
-        <v>536</v>
+      <c r="K158" s="38" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="159" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5950,8 +5920,8 @@
       <c r="H159" s="5"/>
       <c r="I159" s="5"/>
       <c r="J159" s="5"/>
-      <c r="K159" s="43" t="s">
-        <v>537</v>
+      <c r="K159" s="38" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="160" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5975,8 +5945,8 @@
       <c r="H160" s="5"/>
       <c r="I160" s="5"/>
       <c r="J160" s="5"/>
-      <c r="K160" s="43" t="s">
-        <v>538</v>
+      <c r="K160" s="38" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="161" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5999,9 +5969,9 @@
       <c r="G161" s="5"/>
       <c r="H161" s="5"/>
       <c r="I161" s="5"/>
-      <c r="J161" s="44"/>
-      <c r="K161" s="43" t="s">
-        <v>541</v>
+      <c r="J161" s="39"/>
+      <c r="K161" s="38" t="s">
+        <v>530</v>
       </c>
     </row>
     <row r="162" spans="1:11" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6047,8 +6017,8 @@
       <c r="G163" s="5"/>
       <c r="H163" s="5"/>
       <c r="I163" s="5"/>
-      <c r="K163" s="43" t="s">
-        <v>539</v>
+      <c r="K163" s="38" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="164" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6072,8 +6042,8 @@
       <c r="H164" s="5"/>
       <c r="I164" s="5"/>
       <c r="J164" s="5"/>
-      <c r="K164" s="43" t="s">
-        <v>540</v>
+      <c r="K164" s="38" t="s">
+        <v>529</v>
       </c>
     </row>
     <row r="165" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6143,7 +6113,7 @@
       <c r="H167" s="5"/>
       <c r="I167" s="5"/>
       <c r="J167" s="5"/>
-      <c r="K167" s="43" t="s">
+      <c r="K167" s="38" t="s">
         <v>120</v>
       </c>
     </row>
@@ -6366,7 +6336,7 @@
       </c>
       <c r="J179" s="27"/>
       <c r="K179" s="32" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
@@ -6387,7 +6357,7 @@
       </c>
       <c r="J180" s="27"/>
       <c r="K180" s="32" t="s">
-        <v>530</v>
+        <v>519</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
@@ -6408,7 +6378,7 @@
       </c>
       <c r="J181" s="27"/>
       <c r="K181" s="32" t="s">
-        <v>531</v>
+        <v>520</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
@@ -6485,7 +6455,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="24" t="s">
-        <v>523</v>
+        <v>566</v>
       </c>
       <c r="C186" s="15" t="s">
         <v>428</v>
@@ -6750,19 +6720,19 @@
         <v>199</v>
       </c>
       <c r="B200" s="24" t="s">
-        <v>555</v>
+        <v>544</v>
       </c>
       <c r="C200" s="24"/>
       <c r="D200" s="24"/>
       <c r="E200" s="24"/>
       <c r="F200" s="24" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="G200" s="24"/>
       <c r="H200" s="24"/>
       <c r="I200" s="24"/>
       <c r="J200" s="24" t="s">
-        <v>553</v>
+        <v>542</v>
       </c>
       <c r="K200" s="24"/>
       <c r="L200"/>
@@ -6773,25 +6743,25 @@
         <v>200</v>
       </c>
       <c r="B201" s="24" t="s">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="C201" s="24" t="s">
         <v>148</v>
       </c>
       <c r="D201" s="24" t="s">
-        <v>550</v>
+        <v>539</v>
       </c>
       <c r="E201" s="24"/>
       <c r="F201" s="24" t="s">
-        <v>551</v>
+        <v>540</v>
       </c>
       <c r="G201" s="24"/>
       <c r="H201" s="24"/>
       <c r="I201" s="24" t="s">
-        <v>554</v>
+        <v>543</v>
       </c>
       <c r="J201" s="24" t="s">
-        <v>556</v>
+        <v>545</v>
       </c>
       <c r="K201" s="24"/>
       <c r="L201"/>
@@ -6823,23 +6793,23 @@
         <v>202</v>
       </c>
       <c r="B203" s="24" t="s">
-        <v>557</v>
+        <v>546</v>
       </c>
       <c r="C203" s="24" t="s">
         <v>148</v>
       </c>
       <c r="D203" s="24" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="E203" s="24"/>
       <c r="F203" s="24" t="s">
         <v>40</v>
       </c>
       <c r="G203" s="24" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="H203" s="24" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="I203" s="24"/>
       <c r="J203" s="24"/>
@@ -6879,13 +6849,13 @@
         <v>204</v>
       </c>
       <c r="B205" s="24" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="C205" s="24" t="s">
         <v>148</v>
       </c>
       <c r="D205" s="24" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="E205" s="24"/>
       <c r="F205" s="24" t="s">
@@ -6955,26 +6925,26 @@
         <v>208</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>558</v>
+        <v>547</v>
       </c>
       <c r="C209" s="5" t="s">
         <v>148</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>559</v>
+        <v>548</v>
       </c>
       <c r="E209" s="5"/>
       <c r="F209" s="24" t="s">
         <v>40</v>
       </c>
       <c r="G209" s="5" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="H209" s="5" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="I209" s="5" t="s">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="J209" s="5"/>
       <c r="K209" s="24"/>
@@ -7029,26 +6999,26 @@
         <v>212</v>
       </c>
       <c r="B213" s="24" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="C213" s="24" t="s">
         <v>148</v>
       </c>
       <c r="D213" s="5" t="s">
-        <v>559</v>
+        <v>548</v>
       </c>
       <c r="E213" s="24"/>
       <c r="F213" s="24" t="s">
         <v>40</v>
       </c>
       <c r="G213" s="5" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="H213" s="5" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="I213" s="5" t="s">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="J213" s="24"/>
       <c r="K213" s="24"/>
@@ -7060,7 +7030,7 @@
         <v>213</v>
       </c>
       <c r="B214" s="24" t="s">
-        <v>525</v>
+        <v>514</v>
       </c>
       <c r="C214" s="24" t="s">
         <v>148</v>
@@ -7077,7 +7047,7 @@
         <v>214</v>
       </c>
       <c r="B215" s="24" t="s">
-        <v>532</v>
+        <v>521</v>
       </c>
       <c r="C215" s="24" t="s">
         <v>148</v>
@@ -7094,9 +7064,9 @@
         <v>215</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>571</v>
-      </c>
-      <c r="C216" s="47" t="s">
+        <v>560</v>
+      </c>
+      <c r="C216" s="42" t="s">
         <v>486</v>
       </c>
       <c r="D216" s="5"/>
@@ -7112,48 +7082,48 @@
       </c>
       <c r="K216" s="5"/>
     </row>
-    <row r="217" spans="1:13" s="46" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:13" s="41" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A217" s="5">
         <v>216</v>
       </c>
-      <c r="B217" s="45" t="s">
+      <c r="B217" s="40" t="s">
         <v>157</v>
       </c>
-      <c r="C217" s="45" t="s">
+      <c r="C217" s="40" t="s">
         <v>486</v>
       </c>
-      <c r="D217" s="45" t="s">
+      <c r="D217" s="40" t="s">
         <v>158</v>
       </c>
-      <c r="E217" s="45"/>
-      <c r="F217" s="45" t="s">
-        <v>15</v>
-      </c>
-      <c r="G217" s="45"/>
-      <c r="H217" s="45"/>
-      <c r="I217" s="45"/>
-      <c r="J217" s="45"/>
+      <c r="E217" s="40"/>
+      <c r="F217" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="G217" s="40"/>
+      <c r="H217" s="40"/>
+      <c r="I217" s="40"/>
+      <c r="J217" s="40"/>
       <c r="K217" s="24"/>
     </row>
     <row r="218" spans="1:13" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218" s="5">
         <v>217</v>
       </c>
-      <c r="B218" s="42" t="s">
+      <c r="B218" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="C218" s="42" t="s">
+      <c r="C218" s="37" t="s">
         <v>160</v>
       </c>
-      <c r="D218" s="42"/>
-      <c r="E218" s="42"/>
-      <c r="F218" s="42" t="s">
+      <c r="D218" s="37"/>
+      <c r="E218" s="37"/>
+      <c r="F218" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="G218" s="42"/>
-      <c r="H218" s="42"/>
-      <c r="I218" s="42"/>
-      <c r="J218" s="42">
+      <c r="G218" s="37"/>
+      <c r="H218" s="37"/>
+      <c r="I218" s="37"/>
+      <c r="J218" s="37">
         <v>20</v>
       </c>
       <c r="K218" s="24"/>
@@ -7163,19 +7133,19 @@
         <v>218</v>
       </c>
       <c r="B219" s="24" t="s">
-        <v>563</v>
+        <v>552</v>
       </c>
       <c r="C219" s="24"/>
       <c r="D219" s="24"/>
       <c r="E219" s="24"/>
       <c r="F219" s="24" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="G219" s="24"/>
       <c r="H219" s="24"/>
       <c r="I219" s="24"/>
       <c r="J219" s="24" t="s">
-        <v>565</v>
+        <v>554</v>
       </c>
       <c r="K219" s="24"/>
       <c r="L219"/>
@@ -7186,19 +7156,19 @@
         <v>219</v>
       </c>
       <c r="B220" s="24" t="s">
-        <v>511</v>
-      </c>
-      <c r="C220" s="42" t="s">
+        <v>501</v>
+      </c>
+      <c r="C220" s="37" t="s">
         <v>160</v>
       </c>
       <c r="D220" s="24" t="s">
-        <v>564</v>
+        <v>553</v>
       </c>
       <c r="F220" s="24" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
       <c r="I220" s="24" t="s">
-        <v>554</v>
+        <v>543</v>
       </c>
       <c r="K220" s="24" t="s">
         <v>85</v>
@@ -7280,7 +7250,7 @@
         <v>224</v>
       </c>
       <c r="B225" s="24" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="C225" s="24" t="s">
         <v>160</v>
@@ -7311,7 +7281,7 @@
         <v>226</v>
       </c>
       <c r="B227" s="24" t="s">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="C227" s="24" t="s">
         <v>160</v>
@@ -7329,7 +7299,7 @@
         <v>1</v>
       </c>
       <c r="I227" s="24" t="s">
-        <v>567</v>
+        <v>556</v>
       </c>
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.25">
@@ -7357,7 +7327,7 @@
         <v>160</v>
       </c>
       <c r="D229" s="24" t="s">
-        <v>527</v>
+        <v>516</v>
       </c>
       <c r="F229" s="24" t="s">
         <v>15</v>
@@ -7368,7 +7338,7 @@
         <v>229</v>
       </c>
       <c r="B230" s="24" t="s">
-        <v>526</v>
+        <v>515</v>
       </c>
       <c r="C230" s="24" t="s">
         <v>160</v>
@@ -7439,7 +7409,7 @@
         <v>233</v>
       </c>
       <c r="B234" s="24" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="C234" s="24" t="s">
         <v>160</v>
@@ -7470,7 +7440,7 @@
         <v>235</v>
       </c>
       <c r="B236" s="31" t="s">
-        <v>569</v>
+        <v>558</v>
       </c>
       <c r="C236" s="31" t="s">
         <v>160</v>
@@ -7489,7 +7459,7 @@
         <v>1</v>
       </c>
       <c r="I236" s="31" t="s">
-        <v>568</v>
+        <v>557</v>
       </c>
       <c r="J236" s="31"/>
       <c r="K236" s="31"/>
@@ -7499,19 +7469,19 @@
         <v>236</v>
       </c>
       <c r="B237" s="24" t="s">
-        <v>511</v>
-      </c>
-      <c r="C237" s="42" t="s">
+        <v>501</v>
+      </c>
+      <c r="C237" s="37" t="s">
         <v>160</v>
       </c>
       <c r="D237" s="24" t="s">
-        <v>564</v>
+        <v>553</v>
       </c>
       <c r="F237" s="24" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
       <c r="I237" s="24" t="s">
-        <v>554</v>
+        <v>543</v>
       </c>
       <c r="K237" s="24" t="s">
         <v>85</v>
@@ -7584,7 +7554,7 @@
         <v>241</v>
       </c>
       <c r="B242" s="24" t="s">
-        <v>533</v>
+        <v>522</v>
       </c>
       <c r="C242" s="24" t="s">
         <v>486</v>
@@ -7707,7 +7677,7 @@
         <v>247</v>
       </c>
       <c r="B248" s="24" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="C248" s="24" t="s">
         <v>486</v>
@@ -7740,73 +7710,27 @@
       <c r="A250" s="5">
         <v>249</v>
       </c>
-      <c r="B250" s="42" t="s">
+      <c r="B250" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="C250" s="42" t="s">
+      <c r="C250" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="D250" s="42" t="s">
+      <c r="D250" s="37" t="s">
         <v>189</v>
       </c>
-      <c r="E250" s="42"/>
-      <c r="F250" s="42" t="s">
-        <v>15</v>
-      </c>
-      <c r="G250" s="42"/>
-      <c r="H250" s="42"/>
-      <c r="I250" s="42"/>
-      <c r="J250" s="42"/>
-      <c r="K250" s="42"/>
+      <c r="E250" s="37"/>
+      <c r="F250" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="G250" s="37"/>
+      <c r="H250" s="37"/>
+      <c r="I250" s="37"/>
+      <c r="J250" s="37"/>
+      <c r="K250" s="37"/>
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A259" s="5"/>
-    </row>
-    <row r="279" spans="1:11" s="41" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A279" s="5"/>
-      <c r="B279" s="37" t="s">
-        <v>502</v>
-      </c>
-      <c r="C279" s="37" t="s">
-        <v>148</v>
-      </c>
-      <c r="D279" s="37" t="s">
-        <v>495</v>
-      </c>
-      <c r="E279" s="37"/>
-      <c r="F279" s="37" t="s">
-        <v>494</v>
-      </c>
-      <c r="G279" s="37"/>
-      <c r="H279" s="37"/>
-      <c r="I279" s="38" t="s">
-        <v>508</v>
-      </c>
-      <c r="J279" s="39" t="s">
-        <v>509</v>
-      </c>
-      <c r="K279" s="40"/>
-    </row>
-    <row r="280" spans="1:11" s="41" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A280" s="5"/>
-      <c r="B280" s="37" t="s">
-        <v>502</v>
-      </c>
-      <c r="C280" s="37" t="s">
-        <v>148</v>
-      </c>
-      <c r="D280" s="37" t="s">
-        <v>503</v>
-      </c>
-      <c r="E280" s="37"/>
-      <c r="F280" s="42" t="s">
-        <v>15</v>
-      </c>
-      <c r="G280" s="37"/>
-      <c r="H280" s="37"/>
-      <c r="I280" s="16"/>
-      <c r="J280" s="37"/>
-      <c r="K280" s="37"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L250" xr:uid="{7F7ADEC0-586C-43E1-A9C1-2003481904C6}"/>
@@ -7915,16 +7839,16 @@
   <sheetData>
     <row r="1" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>543</v>
+        <v>532</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>22</v>
@@ -7945,13 +7869,13 @@
         <v>30</v>
       </c>
       <c r="K1" s="21" t="s">
-        <v>547</v>
+        <v>536</v>
       </c>
       <c r="L1" s="21" t="s">
-        <v>548</v>
+        <v>537</v>
       </c>
       <c r="M1" s="21" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>31</v>
@@ -7981,16 +7905,16 @@
         <v>54</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="AA1" s="24" t="s">
         <v>64</v>
@@ -7999,7 +7923,7 @@
         <v>69</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>75</v>
@@ -8065,22 +7989,22 @@
         <v>128</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>536</v>
+        <v>525</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>537</v>
+        <v>526</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>538</v>
+        <v>527</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="BE1" s="1" t="s">
         <v>120</v>
@@ -8092,13 +8016,13 @@
         <v>130</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>530</v>
+        <v>519</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="BK1" s="1" t="s">
         <v>150</v>
@@ -8119,7 +8043,7 @@
         <v>330</v>
       </c>
       <c r="BQ1" s="21" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="BR1" s="21" t="s">
         <v>336</v>
@@ -8149,7 +8073,7 @@
         <v>447</v>
       </c>
       <c r="CA1" s="19" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
     </row>
     <row r="2" spans="1:79" x14ac:dyDescent="0.25">
@@ -8160,10 +8084,10 @@
         <v>251</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>546</v>
+        <v>535</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>545</v>
+        <v>534</v>
       </c>
       <c r="E2" t="s">
         <v>190</v>
@@ -8220,7 +8144,7 @@
         <v>200</v>
       </c>
       <c r="W2" s="27" t="s">
-        <v>572</v>
+        <v>561</v>
       </c>
       <c r="X2" s="27" t="s">
         <v>433</v>
@@ -8232,13 +8156,13 @@
         <v>435</v>
       </c>
       <c r="AA2" s="34" t="s">
-        <v>524</v>
+        <v>513</v>
       </c>
       <c r="AB2" t="s">
         <v>206</v>
       </c>
       <c r="AC2" s="27" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="AD2" t="s">
         <v>201</v>
@@ -8304,10 +8228,10 @@
         <v>458</v>
       </c>
       <c r="AZ2" s="35" t="s">
-        <v>534</v>
+        <v>523</v>
       </c>
       <c r="BA2" s="35" t="s">
-        <v>535</v>
+        <v>524</v>
       </c>
       <c r="BB2" s="27" t="s">
         <v>435</v>

--- a/lorenzo-playwright-kdf/excelFramework/testcases/ePMA/LSTP_ePMA_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/ePMA/LSTP_ePMA_WF001.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\ePMA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E1866A5-3075-4329-9AA6-AA0088AFC532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC95D223-8E9C-41EE-8A7A-FDE6EA9BD419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{E0691EBA-01F0-40FD-B574-1F0823951DC7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{E0691EBA-01F0-40FD-B574-1F0823951DC7}"/>
   </bookViews>
   <sheets>
     <sheet name="TestExecution" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="568">
   <si>
     <t>StepNo</t>
   </si>
@@ -1754,6 +1754,9 @@
   </si>
   <si>
     <t>waiting for popup click on button</t>
+  </si>
+  <si>
+    <t>launchRegistration</t>
   </si>
 </sst>
 </file>
@@ -3045,7 +3048,7 @@
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5" t="s">
-        <v>15</v>
+        <v>567</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
@@ -3118,7 +3121,7 @@
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5" t="s">
-        <v>15</v>
+        <v>567</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>

--- a/lorenzo-playwright-kdf/excelFramework/testcases/ePMA/LSTP_ePMA_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/ePMA/LSTP_ePMA_WF001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\ePMA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC95D223-8E9C-41EE-8A7A-FDE6EA9BD419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D94E0E-EF14-49A5-ADD6-C1DFE24DB3DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{E0691EBA-01F0-40FD-B574-1F0823951DC7}"/>
   </bookViews>
@@ -7162,7 +7162,7 @@
         <v>501</v>
       </c>
       <c r="C220" s="37" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="D220" s="24" t="s">
         <v>553</v>
@@ -7475,7 +7475,7 @@
         <v>501</v>
       </c>
       <c r="C237" s="37" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="D237" s="24" t="s">
         <v>553</v>
